--- a/tests/fixtures/reserves.xlsx
+++ b/tests/fixtures/reserves.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Provisions" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Controls" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -106,8 +106,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -307,17 +311,17 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>1.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -341,22 +345,22 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <f aca="false">Hypotheses!B12 * 1000</f>
         <v>1750</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <f aca="false">C5 * 0.035</f>
         <v>61.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="e">
+      <c r="C7" s="1" t="e">
         <f aca="false">VLOOKUP(B13,sometable,2,FALSE())</f>
         <v>#NAME?</v>
       </c>
@@ -381,7 +385,7 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D1" s="0" t="e">
+      <c r="D1" s="1" t="e">
         <f aca="false">SUM(Provisions!C5:C7)</f>
         <v>#NAME?</v>
       </c>
